--- a/04_DESIGN_TABLES/DesignTable_6600.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6600.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1791,6 +1796,9 @@
       <c r="I20" t="n">
         <v>1.31</v>
       </c>
+      <c r="J20" t="n">
+        <v>1.312</v>
+      </c>
       <c r="K20" t="n">
         <v>1.875</v>
       </c>
@@ -1812,17 +1820,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Air-Way s193 only (double-pass 20 rows)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] Air-Way s193 only (double-pass 20 rows) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): D3@BORE: Brennan TFA catalog p57 table TFA-p057-t01 (MJ-MJ-FJS TEE) row 6600-24-24-24-FG column 'A3 DRILL' = 1.312 (catalog_verified.json); Air-Way s193 printed ".31" (garbled, cell left empty; Q-GARBLE) - consistent with 1.31, the siblings D1 / D2 1.31; OMi Items row 2080: no ID; no own STEP; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>D (3) printed ".31" on Air-Way (siblings 1.31); copied as printed | D (3): printed ".31" (not a clean decimal) -&gt; left empty, MISSING</t>
+          <t>D (3) printed ".31" on Air-Way (siblings 1.31); copied as printed | D (3): printed ".31" (not a clean decimal) -&gt; left empty, MISSING | BRENNAN-ONLY (2026-10-18) for D3 only (Brennan 1.312 = Air-Way '.31' read as 1.31). Kept Air-Way where Brennan differs: M10@DRIVE Air-Way 1.86 vs Brennan M4 LGTH 1.870</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -1833,6 +1841,11 @@
       <c r="T20" t="inlineStr">
         <is>
           <t>6600-24-24-24-FG</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
